--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/post DFS_HRM-2031-0360/Panel 02/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/post DFS_HRM-2031-0360/Panel 02/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,28 +454,23 @@
           <t>Unit 7</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Pad 1</t>
-        </is>
-      </c>
       <c r="C2" t="n">
-        <v>16.94288</v>
+        <v>17.04457</v>
       </c>
       <c r="D2" t="n">
-        <v>16.75545</v>
+        <v>16.43523</v>
       </c>
       <c r="E2" t="n">
-        <v>16.6903</v>
+        <v>16.65829</v>
       </c>
       <c r="F2" t="n">
-        <v>41.76588</v>
+        <v>42.14218</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05064</v>
+        <v>0.05088</v>
       </c>
       <c r="H2" t="n">
-        <v>1.82504</v>
+        <v>1.79509</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +480,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.61763</v>
+        <v>16.82523</v>
       </c>
       <c r="D3" t="n">
-        <v>16.46557</v>
+        <v>16.52074</v>
       </c>
       <c r="E3" t="n">
-        <v>16.50061</v>
+        <v>16.75321</v>
       </c>
       <c r="F3" t="n">
-        <v>42.08374</v>
+        <v>42.19198</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05091</v>
+        <v>0.05028</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84187</v>
+        <v>1.8334</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +505,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.93735</v>
+        <v>16.69942</v>
       </c>
       <c r="D4" t="n">
-        <v>16.9215</v>
+        <v>16.25244</v>
       </c>
       <c r="E4" t="n">
-        <v>16.6816</v>
+        <v>16.38345</v>
       </c>
       <c r="F4" t="n">
-        <v>42.82154</v>
+        <v>43.37499</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05039</v>
+        <v>0.05019</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83814</v>
+        <v>1.81381</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +530,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.9492</v>
+        <v>16.78458</v>
       </c>
       <c r="D5" t="n">
-        <v>16.73127</v>
+        <v>16.47985</v>
       </c>
       <c r="E5" t="n">
-        <v>16.91228</v>
+        <v>16.7392</v>
       </c>
       <c r="F5" t="n">
-        <v>42.37464</v>
+        <v>42.55944</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04985</v>
+        <v>0.05002</v>
       </c>
       <c r="H5" t="n">
-        <v>1.83844</v>
+        <v>1.77474</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +555,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.73941</v>
+        <v>16.77384</v>
       </c>
       <c r="D6" t="n">
-        <v>16.61526</v>
+        <v>16.5141</v>
       </c>
       <c r="E6" t="n">
-        <v>16.84384</v>
+        <v>16.69159</v>
       </c>
       <c r="F6" t="n">
-        <v>42.55057</v>
+        <v>42.49736</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04974</v>
+        <v>0.05064</v>
       </c>
       <c r="H6" t="n">
-        <v>1.80598</v>
+        <v>1.83542</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +580,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.4204</v>
+        <v>16.9352</v>
       </c>
       <c r="D7" t="n">
-        <v>16.55533</v>
+        <v>16.85682</v>
       </c>
       <c r="E7" t="n">
-        <v>16.37848</v>
+        <v>16.90675</v>
       </c>
       <c r="F7" t="n">
-        <v>41.62279</v>
+        <v>41.72712</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04955</v>
+        <v>0.04999</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8415</v>
+        <v>1.83344</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +605,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.64924</v>
+        <v>16.98108</v>
       </c>
       <c r="D8" t="n">
-        <v>16.69312</v>
+        <v>16.53495</v>
       </c>
       <c r="E8" t="n">
-        <v>16.67471</v>
+        <v>16.93515</v>
       </c>
       <c r="F8" t="n">
-        <v>42.53465</v>
+        <v>42.19522</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05085</v>
+        <v>0.05076</v>
       </c>
       <c r="H8" t="n">
-        <v>1.83268</v>
+        <v>1.83279</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +630,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.84521</v>
+        <v>17.05217</v>
       </c>
       <c r="D9" t="n">
-        <v>16.65566</v>
+        <v>16.6082</v>
       </c>
       <c r="E9" t="n">
-        <v>16.99186</v>
+        <v>17.00311</v>
       </c>
       <c r="F9" t="n">
-        <v>42.66608</v>
+        <v>42.2677</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05101</v>
+        <v>0.04991</v>
       </c>
       <c r="H9" t="n">
-        <v>1.82007</v>
+        <v>1.82513</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +655,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.84852</v>
+        <v>16.90969</v>
       </c>
       <c r="D10" t="n">
-        <v>16.79292</v>
+        <v>16.236</v>
       </c>
       <c r="E10" t="n">
-        <v>16.5759</v>
+        <v>16.75845</v>
       </c>
       <c r="F10" t="n">
-        <v>42.46301</v>
+        <v>42.65377</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05034</v>
+        <v>0.0509</v>
       </c>
       <c r="H10" t="n">
-        <v>1.80864</v>
+        <v>1.83328</v>
       </c>
     </row>
     <row r="11">
@@ -722,22 +717,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.41506</v>
+        <v>16.84157</v>
       </c>
       <c r="D12" t="n">
-        <v>16.32125</v>
+        <v>16.356</v>
       </c>
       <c r="E12" t="n">
-        <v>16.80527</v>
+        <v>16.59547</v>
       </c>
       <c r="F12" t="n">
-        <v>42.49719</v>
+        <v>41.6659</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05079</v>
+        <v>0.05065</v>
       </c>
       <c r="H12" t="n">
-        <v>1.84248</v>
+        <v>1.8164</v>
       </c>
     </row>
     <row r="13">
@@ -747,22 +742,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.30858</v>
+        <v>17.27928</v>
       </c>
       <c r="D13" t="n">
-        <v>16.34153</v>
+        <v>16.56681</v>
       </c>
       <c r="E13" t="n">
-        <v>16.63642</v>
+        <v>16.74059</v>
       </c>
       <c r="F13" t="n">
-        <v>43.34261</v>
+        <v>42.55961</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05103</v>
+        <v>0.05112</v>
       </c>
       <c r="H13" t="n">
-        <v>1.8627</v>
+        <v>1.83777</v>
       </c>
     </row>
     <row r="14">
@@ -772,22 +767,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.9872</v>
+        <v>17.03736</v>
       </c>
       <c r="D14" t="n">
-        <v>16.81994</v>
+        <v>16.30143</v>
       </c>
       <c r="E14" t="n">
-        <v>16.48227</v>
+        <v>16.6664</v>
       </c>
       <c r="F14" t="n">
-        <v>43.25767</v>
+        <v>41.06438</v>
       </c>
       <c r="G14" t="n">
-        <v>0.04927</v>
+        <v>0.05125</v>
       </c>
       <c r="H14" t="n">
-        <v>1.80252</v>
+        <v>1.82002</v>
       </c>
     </row>
     <row r="15">
@@ -797,22 +792,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.85976</v>
+        <v>17.06537</v>
       </c>
       <c r="D15" t="n">
-        <v>16.89132</v>
+        <v>16.39805</v>
       </c>
       <c r="E15" t="n">
-        <v>16.84018</v>
+        <v>16.85123</v>
       </c>
       <c r="F15" t="n">
-        <v>42.68281</v>
+        <v>42.78007</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0519</v>
+        <v>0.05153</v>
       </c>
       <c r="H15" t="n">
-        <v>1.83435</v>
+        <v>1.81115</v>
       </c>
     </row>
     <row r="16">
@@ -822,22 +817,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.44459</v>
+        <v>16.83909</v>
       </c>
       <c r="D16" t="n">
-        <v>16.4976</v>
+        <v>16.75574</v>
       </c>
       <c r="E16" t="n">
-        <v>16.54995</v>
+        <v>16.79006</v>
       </c>
       <c r="F16" t="n">
-        <v>42.82267</v>
+        <v>41.80828</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05014</v>
+        <v>0.05121</v>
       </c>
       <c r="H16" t="n">
-        <v>1.77939</v>
+        <v>1.82974</v>
       </c>
     </row>
     <row r="17">
@@ -847,22 +842,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.60743</v>
+        <v>16.76976</v>
       </c>
       <c r="D17" t="n">
-        <v>16.69373</v>
+        <v>16.55399</v>
       </c>
       <c r="E17" t="n">
-        <v>16.62478</v>
+        <v>16.62008</v>
       </c>
       <c r="F17" t="n">
-        <v>42.67294</v>
+        <v>42.40175</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0502</v>
+        <v>0.04968</v>
       </c>
       <c r="H17" t="n">
-        <v>1.86529</v>
+        <v>1.79392</v>
       </c>
     </row>
     <row r="18">
@@ -872,22 +867,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.38918</v>
+        <v>16.86707</v>
       </c>
       <c r="D18" t="n">
-        <v>16.25359</v>
+        <v>16.55106</v>
       </c>
       <c r="E18" t="n">
-        <v>16.61692</v>
+        <v>16.5837</v>
       </c>
       <c r="F18" t="n">
-        <v>42.62387</v>
+        <v>42.39018</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05052</v>
+        <v>0.0504</v>
       </c>
       <c r="H18" t="n">
-        <v>1.77487</v>
+        <v>1.82827</v>
       </c>
     </row>
     <row r="19">
@@ -897,22 +892,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.75579</v>
+        <v>16.84069</v>
       </c>
       <c r="D19" t="n">
-        <v>16.39285</v>
+        <v>16.46438</v>
       </c>
       <c r="E19" t="n">
-        <v>16.929</v>
+        <v>16.55422</v>
       </c>
       <c r="F19" t="n">
-        <v>42.43665</v>
+        <v>42.65756</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05089</v>
+        <v>0.05094</v>
       </c>
       <c r="H19" t="n">
-        <v>1.82672</v>
+        <v>1.83339</v>
       </c>
     </row>
     <row r="20">
@@ -922,156 +917,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.60644</v>
+        <v>16.72027</v>
       </c>
       <c r="D20" t="n">
-        <v>16.52909</v>
+        <v>16.63395</v>
       </c>
       <c r="E20" t="n">
-        <v>16.65398</v>
+        <v>16.64911</v>
       </c>
       <c r="F20" t="n">
-        <v>41.67726</v>
+        <v>42.60634</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05024</v>
+        <v>0.05122</v>
       </c>
       <c r="H20" t="n">
-        <v>1.83787</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>via 1</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>0.59916</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1.12035</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>0.5887</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1.13909</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Unit 9</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>0.6002999999999999</v>
-      </c>
-      <c r="D24" t="n">
-        <v>1.1338</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Unit 4</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>0.60218</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1.10845</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Unit 5</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>0.61143</v>
-      </c>
-      <c r="D26" t="n">
-        <v>1.10692</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>0.60143</v>
-      </c>
-      <c r="D27" t="n">
-        <v>1.08184</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>0.5994699999999999</v>
-      </c>
-      <c r="D28" t="n">
-        <v>1.0954</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>0.60889</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1.12578</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>0.60195</v>
-      </c>
-      <c r="D30" t="n">
-        <v>1.12525</v>
+        <v>1.85641</v>
       </c>
     </row>
   </sheetData>
